--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90852</v>
+        <v>90858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90858</v>
+        <v>90862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90882</v>
+        <v>90892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90892</v>
+        <v>90893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90893</v>
+        <v>90896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90896</v>
+        <v>90901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90901</v>
+        <v>90912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90912</v>
+        <v>90913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90913</v>
+        <v>90916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37339-2026 artfynd.xlsx
+++ b/artfynd/A 37339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137090474</v>
       </c>
       <c r="B2" t="n">
-        <v>90916</v>
+        <v>90920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
